--- a/monitor_xlsx/20260311.xlsx
+++ b/monitor_xlsx/20260311.xlsx
@@ -544,10 +544,6 @@
           <t>+1.79%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-1.37%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>-0.10%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+0.63%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>-2.81%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>+12.08%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -695,7 +671,6 @@
           <t>371.81億</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>-481.15億</t>
@@ -733,7 +708,6 @@
           <t>40.54億</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>104.55億</t>
@@ -744,8 +718,6 @@
           <t>522.75億</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -763,15 +735,11 @@
           <t>163.58%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>131.73%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -789,11 +757,6 @@
           <t>520.09億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -811,15 +774,11 @@
           <t>12693口</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>13787口</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,7 +796,6 @@
           <t>-82.04億</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>-7.31億</t>
@@ -942,10 +900,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1067,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1102,6 +1056,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1293,7 +1248,6 @@
           <t>S&amp;P黃金正2</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="G5" s="7" t="n">
         <v>22</v>
       </c>
@@ -2262,6 +2216,165 @@
       <c r="W20" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>962</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>826</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-208</v>
+      </c>
+      <c r="G21" t="n">
+        <v>404</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>12</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>77</v>
+      </c>
+      <c r="L21" t="n">
+        <v>85</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>624</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-59</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>263</v>
+      </c>
+      <c r="J22" t="n">
+        <v>82</v>
+      </c>
+      <c r="K22" t="n">
+        <v>23</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-250</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1495</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1745</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>239</v>
+      </c>
+      <c r="G23" t="n">
+        <v>849</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>347</v>
+      </c>
+      <c r="J23" t="n">
+        <v>33</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3114</v>
+      </c>
+      <c r="L23" t="n">
+        <v>15803</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-106246</v>
+      </c>
+      <c r="N23" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>偏多</t>
         </is>
       </c>
     </row>

--- a/monitor_xlsx/20260311.xlsx
+++ b/monitor_xlsx/20260311.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2378,6 +2378,59 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>德律</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>253</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9176</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>-330</v>
+      </c>
+      <c r="G24" t="n">
+        <v>436</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>110</v>
+      </c>
+      <c r="J24" t="n">
+        <v>123</v>
+      </c>
+      <c r="K24" t="n">
+        <v>7365</v>
+      </c>
+      <c r="L24" t="n">
+        <v>35347</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-58883</v>
+      </c>
+      <c r="N24" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
